--- a/relatorios_simplificados/separarNeotin_SIMPLIFICADO.xlsx
+++ b/relatorios_simplificados/separarNeotin_SIMPLIFICADO.xlsx
@@ -426,140 +426,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Paciente RJ - São João de Meriti</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RJ - São João de Meriti</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Quantidade RJ - São João de Meriti</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Paciente RJ - Queimados</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>RJ - Queimados</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Quantidade RJ - Queimados</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Paciente RJ - Belford Roxo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>RJ - Belford Roxo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Quantidade RJ - Belford Roxo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Paciente RJ - Duque de Caxias</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>RJ - Duque de Caxias</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Quantidade RJ - Duque de Caxias</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Paciente RJ - Itaguaí</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>RJ - Itaguaí</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Quantidade RJ - Itaguaí</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Paciente RJ - Magé</t>
+          <t>Paciente RJ - Nilópolis</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>RJ - Magé</t>
+          <t>RJ - Nilópolis</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Quantidade RJ - Magé</t>
+          <t>Quantidade RJ - Nilópolis</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Paciente RJ - Nilópolis</t>
+          <t>Paciente RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Quantidade RJ - Nilópolis</t>
+          <t>Quantidade RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Paciente RJ - Nova Iguaçu</t>
+          <t>Paciente RJ - Japeri</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>RJ - Nova Iguaçu</t>
+          <t>RJ - Japeri</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Quantidade RJ - Nova Iguaçu</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Paciente RJ - Queimados</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>RJ - Queimados</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Quantidade RJ - Queimados</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Paciente RJ - Seropédica</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>RJ - Seropédica</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Quantidade RJ - Seropédica</t>
+          <t>Quantidade RJ - Japeri</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DERICK CARDOZO DE OLIVEIRA</t>
+          <t>MARIA NEILA DE SOUSA BARROS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -567,12 +537,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BERNARDO GUILHERME SOUZA DOS SANTOS</t>
+          <t>JOSIAS GOMES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -580,12 +550,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NICKOLAS DA SILVA LOURENCO</t>
+          <t>NICE BATALHA RIBEIRO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -593,12 +563,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>NYCOLAS SANCHES FIALHO</t>
+          <t>MILDNA BERNARDO REZENDE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -606,12 +576,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>LORENZO ALVES TAVARES</t>
+          <t>CLAUDIA LUCIA VIEIRA DE SOUZA</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -619,53 +589,27 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>KEROLLAYNE VITORIA DA COSTA SILVA</t>
+          <t>LIDIANE PINTO ROSA GOUDARD</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>HERNIOPLASTIA UMBILICAL - PEDIATRICO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>PEDRO LUCCA BARBOSA RAMOS</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>HERNIOPLASTIA INGUINAL (BILATERAL) - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>CALEBE LEONARDO DA SILVA MACEDO DE SANTANA</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
-        </is>
-      </c>
-      <c r="X2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DERICK CARDOZO DE OLIVEIRA</t>
+          <t>LIETE PEREIRA DE LIMA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -673,12 +617,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ESTHER LEMOS VIEIRA</t>
+          <t>JOSIAS GOMES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -686,12 +630,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ISABELLA LIMA DOMINGOS DA SILVA</t>
+          <t>RAYSSA SANTANA NASCIMENTO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -699,12 +643,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>EMANUELLY VITORIA AZEVEDO MARTINS</t>
+          <t>SUENIL DE OLIVEIRA GOMES</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -712,59 +656,53 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>LORENZO ALVES TAVARES</t>
+          <t>LEILA DOS SANTOS</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>PIETRO COELHO DE AZEVEDO</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>ORQUIDOPEXIA BILATERAL - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>CALEBE LEONARDO DA SILVA MACEDO DE SANTANA</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="X3" t="n">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>LEANDRO DA SILVA CONCEICAO</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NORMA FONSECA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GUSTAVO MENDES PEREIRA</t>
+          <t>JOSIAS GOMES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -772,12 +710,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MIGUEL BARBOSA SIMAO SCHNEIDER</t>
+          <t>THIAGO PEREIRA CASSIANO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -785,55 +723,69 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>VALENTINA ROQUE DE CARVALHO</t>
+          <t>RENATHA MENDES DA SILVA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>LEILA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>LIDIANE PINTO ROSA GOUDARD</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ANA SOPHIA GOMES DE SOUZA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REGINA FATIMA SILVA FERREIRA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DAVI MOREIRA APOLINARIO</t>
+          <t>SOLANGE AGOSTINHO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -841,55 +793,69 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>GUSTAVO DA SILVA MIRANDA</t>
+          <t>RENATHA MENDES DA SILVA</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>CLAUDIA LUCIA VIEIRA DE SOUZA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>LEANDRO DA SILVA CONCEICAO</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>GABRIEL LUCAS HEGENDORNE ALMEIDA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MARIA NEILA DE SOUSA BARROS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SOPHIA VALENTINA SANTA BRIGIDA SANCHES</t>
+          <t>RAYSSA SANTANA NASCIMENTO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -897,55 +863,69 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>GIOVANNA DA COSTA CASTILHO</t>
+          <t>SUENIL DE OLIVEIRA GOMES</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO CIRURGIA GERAL</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>CINTIA HONORATO SILVA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>LEANDRO DA SILVA CONCEICAO</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>THAYLLA DA SILVA DOS SANTOS</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REGINA FATIMA SILVA FERREIRA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ISABELLA LIMA DOMINGOS DA SILVA</t>
+          <t>THIAGO PEREIRA CASSIANO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -953,55 +933,69 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>LUIZ FELIPE ZARANZA DA SILVA</t>
+          <t>JOSE HENRIQUE RODRIGUES</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO CIRURGIA GERAL</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>LEILA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>LEANDRO DA SILVA CONCEICAO</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA EPIGASTRICA - ADULTO</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MIRELLA OLIVEIRA CARDOSO SILVA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MARIA NEILA DE SOUSA BARROS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MIGUEL BARBOSA SIMAO SCHNEIDER</t>
+          <t>SARA LINO DA SILVA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ADENOIDECTOMIA PEDIÁTRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1009,55 +1003,69 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>NYCOLAS SANCHES FIALHO</t>
+          <t>CHRISTIANE PEREIRA DA SILVA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ORQUIDOPEXIA BILATERAL - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>CLAUDIA LUCIA VIEIRA DE SOUZA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>LIDIANE PINTO ROSA GOUDARD</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>THAYLLA DA SILVA DOS SANTOS</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>REGINA FATIMA SILVA FERREIRA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NICKOLAS DA SILVA LOURENCO</t>
+          <t>JOANA D ARC MOURA DA SILVA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1065,12 +1073,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>EMANUELLY VITORIA AZEVEDO MARTINS</t>
+          <t>MILDNA BERNARDO REZENDE</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1082,38 +1090,32 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>MIRELLA OLIVEIRA CARDOSO SILVA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>JOSE ROBSON DA SILVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SOPHIA VALENTINA SANTA BRIGIDA SANCHES</t>
+          <t>MANOEL DA SILVA ARRUDA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1121,12 +1123,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>JOSE BENICIO TOLEDO</t>
+          <t>MILDNA BERNARDO REZENDE</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ORQUIDOPEXIA BILATERAL - PEDIATRICO</t>
+          <t>CIRURGIA DE HERNIOPLASTIA INGUINAL (UNILATERAL) - ADULTO</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1138,41 +1140,45 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>GABRIEL LUCAS HEGENDORNE ALMEIDA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MARCELO RIBEIRO DA SILVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SARA LINO DA SILVA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>GIOVANNA DA COSTA CASTILHO</t>
+          <t>SUENIL DE OLIVEIRA GOMES</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>HERNIOPLASTIA UMBILICAL - PEDIATRICO</t>
+          <t>CIRURGIA DE HERNIOPLASTIA INGUINAL (UNILATERAL) - ADULTO</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1184,41 +1190,45 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ANA SOPHIA GOMES DE SOUZA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CELIA DOS SANTOS PEDREIRO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>THIAGO PEREIRA CASSIANO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>JOSE BENICIO TOLEDO</t>
+          <t>RENATHA MENDES DA SILVA</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>POSTECTOMIA - PEDIATRICO</t>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1230,69 +1240,87 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ESTHER LEMOS VIEIRA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SUELI DO AMARAL RIBEIRO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SARA LINO DA SILVA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>SUENIL DE OLIVEIRA GOMES</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>BERNARDO GUILHERME SOUZA DOS SANTOS</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FRANCISCO DAS CHAGAS MORAIS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>RAYSSA SANTANA NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1302,12 +1330,456 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ROZANA FERREIRA EGIDIO ALVES PINTO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VALQUIRIA DOS SANTOS SILVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MARIA DE LOURDES DE SA VIANA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>JOSE ROBSON DA SILVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MARCELO RIBEIRO DA SILVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ROZANA FERREIRA EGIDIO ALVES PINTO</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SUELI DO AMARAL RIBEIRO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FRANCISCO DAS CHAGAS MORAIS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CELIA DOS SANTOS PEDREIRO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CELIA DOS SANTOS PEDREIRO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FRANCISCO DAS CHAGAS MORAIS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA INCISIONAL - ADULTO</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SUELI DO AMARAL RIBEIRO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ROZANA FERREIRA EGIDIO ALVES PINTO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MARCELO RIBEIRO DA SILVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA INCISIONAL - ADULTO</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>JOSE ROBSON DA SILVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1320,7 +1792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1383,27 +1855,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19/12/2025 13:00</t>
+          <t>02/04/2026 13:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DERICK CARDOZO DE OLIVEIRA</t>
+          <t>MARIA NEILA DE SOUSA BARROS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12/12/2014</t>
+          <t>01/05/1978</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1411,7 +1883,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1431,34 +1903,34 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16/01/2026 08:00</t>
+          <t>02/04/2026 13:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DERICK CARDOZO DE OLIVEIRA</t>
+          <t>LIETE PEREIRA DE LIMA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12/12/2014</t>
+          <t>29/03/1951</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1466,7 +1938,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>R$ 6.514,54</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1481,39 +1953,39 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>R$ 1.183,81</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>R$ 7.698,35</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RJ - Duque de Caxias</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19/12/2025 13:00</t>
+          <t>02/04/2026 13:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BERNARDO GUILHERME SOUZA DOS SANTOS</t>
+          <t>NORMA FONSECA DOS SANTOS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>06/09/2019</t>
+          <t>05/07/1960</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1521,7 +1993,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1541,34 +2013,34 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RJ - Duque de Caxias</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19/12/2025 13:00</t>
+          <t>02/04/2026 13:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ESTHER LEMOS VIEIRA</t>
+          <t>REGINA FATIMA SILVA FERREIRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01/09/2016</t>
+          <t>11/03/1962</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1576,7 +2048,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1596,34 +2068,34 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RJ - Duque de Caxias</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19/12/2025 13:00</t>
+          <t>14/04/2026 10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GUSTAVO MENDES PEREIRA</t>
+          <t>MARIA NEILA DE SOUSA BARROS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12/06/2016</t>
+          <t>01/05/1978</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1631,7 +2103,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 5.740,01</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1646,39 +2118,39 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 434,99</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 6.175,00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RJ - Duque de Caxias</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19/12/2025 13:00</t>
+          <t>14/04/2026 10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ANA SOPHIA GOMES DE SOUZA</t>
+          <t>REGINA FATIMA SILVA FERREIRA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>04/01/2019</t>
+          <t>11/03/1962</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1686,7 +2158,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 5.740,01</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1701,39 +2173,39 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 434,99</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 6.175,00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RJ - Duque de Caxias</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19/12/2025 13:00</t>
+          <t>02/04/2026 07:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GABRIEL LUCAS HEGENDORNE ALMEIDA</t>
+          <t>MARIA NEILA DE SOUSA BARROS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15/02/2016</t>
+          <t>01/05/1978</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1741,7 +2213,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1761,34 +2233,34 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RJ - Duque de Caxias</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22/12/2025 15:00</t>
+          <t>02/04/2026 07:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>THAYLLA DA SILVA DOS SANTOS</t>
+          <t>REGINA FATIMA SILVA FERREIRA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12/07/2012</t>
+          <t>11/03/1962</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1796,7 +2268,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1816,34 +2288,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RJ - Duque de Caxias</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22/12/2025 15:00</t>
+          <t>08/04/2026 07:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MIRELLA OLIVEIRA CARDOSO SILVA</t>
+          <t>JOSE ROBSON DA SILVA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>03/10/2020</t>
+          <t>16/07/1964</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1851,7 +2323,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1871,34 +2343,34 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RJ - Duque de Caxias</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>07/01/2026 08:00</t>
+          <t>08/04/2026 07:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>THAYLLA DA SILVA DOS SANTOS</t>
+          <t>MARCELO RIBEIRO DA SILVA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12/07/2012</t>
+          <t>05/05/1979</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1906,7 +2378,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>R$ 6.514,54</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1921,39 +2393,39 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>R$ 1.183,81</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R$ 7.698,35</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RJ - Duque de Caxias</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>07/01/2026 08:00</t>
+          <t>09/04/2026 07:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MIRELLA OLIVEIRA CARDOSO SILVA</t>
+          <t>CELIA DOS SANTOS PEDREIRO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>03/10/2020</t>
+          <t>31/12/1962</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1961,7 +2433,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>R$ 6.514,54</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1976,39 +2448,39 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>R$ 1.183,81</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R$ 7.698,35</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RJ - Duque de Caxias</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11/01/2026 08:00</t>
+          <t>09/04/2026 07:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GABRIEL LUCAS HEGENDORNE ALMEIDA</t>
+          <t>SUELI DO AMARAL RIBEIRO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15/02/2016</t>
+          <t>24/04/1963</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -2016,7 +2488,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>R$ 6.514,54</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2031,39 +2503,39 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>R$ 1.183,81</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R$ 7.698,35</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RJ - Duque de Caxias</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11/01/2026 08:00</t>
+          <t>09/04/2026 07:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ANA SOPHIA GOMES DE SOUZA</t>
+          <t>FRANCISCO DAS CHAGAS MORAIS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>04/01/2019</t>
+          <t>17/11/1963</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2071,7 +2543,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>R$ 6.514,54</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2086,39 +2558,39 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>R$ 1.183,81</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R$ 7.698,35</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RJ - Duque de Caxias</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11/01/2026 08:00</t>
+          <t>09/04/2026 07:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ESTHER LEMOS VIEIRA</t>
+          <t>ROZANA FERREIRA EGIDIO ALVES PINTO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>01/09/2016</t>
+          <t>30/11/1963</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -2126,7 +2598,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>R$ 6.514,54</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2141,39 +2613,39 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>R$ 1.183,81</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R$ 7.698,35</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RJ - Duque de Caxias</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16/01/2026 08:00</t>
+          <t>01/04/2026 16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BERNARDO GUILHERME SOUZA DOS SANTOS</t>
+          <t>VALQUIRIA DOS SANTOS SILVA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>06/09/2019</t>
+          <t>19/11/1976</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -2181,7 +2653,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>R$ 6.514,54</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2196,39 +2668,39 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>R$ 1.183,81</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R$ 7.698,35</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RJ - Itaguaí</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19/12/2025 13:00</t>
+          <t>01/04/2026 16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NICKOLAS DA SILVA LOURENCO</t>
+          <t>MARIA DE LOURDES DE SA VIANA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>03/05/2014</t>
+          <t>28/08/1965</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2236,7 +2708,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2256,34 +2728,34 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RJ - Itaguaí</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19/12/2025 13:00</t>
+          <t>01/04/2026 16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ISABELLA LIMA DOMINGOS DA SILVA</t>
+          <t>JOSE ROBSON DA SILVA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27/11/2015</t>
+          <t>16/07/1964</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2291,7 +2763,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2311,34 +2783,34 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RJ - Itaguaí</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19/12/2025 13:00</t>
+          <t>01/04/2026 16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MIGUEL BARBOSA SIMAO SCHNEIDER</t>
+          <t>MARCELO RIBEIRO DA SILVA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19/02/2014</t>
+          <t>05/05/1979</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -2346,7 +2818,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2366,34 +2838,34 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RJ - Itaguaí</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22/12/2025 15:00</t>
+          <t>08/04/2026 16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DAVI MOREIRA APOLINARIO</t>
+          <t>ROZANA FERREIRA EGIDIO ALVES PINTO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>24/07/2012</t>
+          <t>30/11/1963</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -2401,7 +2873,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2421,34 +2893,34 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RJ - Itaguaí</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22/12/2025 15:00</t>
+          <t>08/04/2026 16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SOPHIA VALENTINA SANTA BRIGIDA SANCHES</t>
+          <t>SUELI DO AMARAL RIBEIRO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10/10/2017</t>
+          <t>24/04/1963</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -2456,7 +2928,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2476,34 +2948,34 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RJ - Itaguaí</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09/01/2026 09:00</t>
+          <t>08/04/2026 16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ISABELLA LIMA DOMINGOS DA SILVA</t>
+          <t>FRANCISCO DAS CHAGAS MORAIS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>27/11/2015</t>
+          <t>17/11/1963</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2511,7 +2983,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R$ 6.514,54</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2526,39 +2998,39 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>R$ 1.183,81</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>R$ 7.698,35</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RJ - Itaguaí</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10/01/2026 08:00</t>
+          <t>08/04/2026 16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MIGUEL BARBOSA SIMAO SCHNEIDER</t>
+          <t>CELIA DOS SANTOS PEDREIRO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19/02/2014</t>
+          <t>31/12/1962</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ADENOIDECTOMIA PEDIÁTRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -2566,7 +3038,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R$ 4.250,90</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2581,39 +3053,39 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>R$ 1.079,10</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>R$ 5.330,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RJ - Itaguaí</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10/01/2026 08:00</t>
+          <t>17/04/2026 08:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NICKOLAS DA SILVA LOURENCO</t>
+          <t>CELIA DOS SANTOS PEDREIRO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>03/05/2014</t>
+          <t>31/12/1962</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -2621,7 +3093,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R$ 6.514,54</t>
+          <t>R$ 5.740,01</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2636,39 +3108,39 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>R$ 1.183,81</t>
+          <t>R$ 434,99</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>R$ 7.698,35</t>
+          <t>R$ 6.175,00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RJ - Itaguaí</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17/01/2026 08:00</t>
+          <t>17/04/2026 08:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SOPHIA VALENTINA SANTA BRIGIDA SANCHES</t>
+          <t>FRANCISCO DAS CHAGAS MORAIS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10/10/2017</t>
+          <t>17/11/1963</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>CIRURGIA DE HERNIOPLASTIA INCISIONAL - ADULTO</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2676,7 +3148,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>R$ 6.514,54</t>
+          <t>R$ 5.635,08</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2691,39 +3163,39 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>R$ 1.183,81</t>
+          <t>R$ 539,92</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>R$ 7.698,35</t>
+          <t>R$ 6.175,00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RJ - Magé</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17/12/2025 09:00</t>
+          <t>17/04/2026 08:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NYCOLAS SANCHES FIALHO</t>
+          <t>SUELI DO AMARAL RIBEIRO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>23/06/2014</t>
+          <t>24/04/1963</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO CIRURGIA GERAL</t>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2731,7 +3203,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 5.740,01</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2746,39 +3218,39 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 434,99</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 6.175,00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RJ - Magé</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>05/01/2026 13:00</t>
+          <t>17/04/2026 08:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EMANUELLY VITORIA AZEVEDO MARTINS</t>
+          <t>ROZANA FERREIRA EGIDIO ALVES PINTO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>02/11/2018</t>
+          <t>30/11/1963</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2786,7 +3258,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 5.740,01</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2801,39 +3273,39 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 434,99</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 6.175,00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RJ - Magé</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>05/01/2026 13:00</t>
+          <t>10/04/2026 11:11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VALENTINA ROQUE DE CARVALHO</t>
+          <t>MARCELO RIBEIRO DA SILVA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>05/03/2018</t>
+          <t>05/05/1979</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>CIRURGIA DE HERNIOPLASTIA INCISIONAL - ADULTO</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2841,7 +3313,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 5.635,08</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2856,39 +3328,39 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 539,92</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 6.175,00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RJ - Magé</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>05/01/2026 13:00</t>
+          <t>18/04/2026 08:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GUSTAVO DA SILVA MIRANDA</t>
+          <t>JOSE ROBSON DA SILVA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>09/12/2013</t>
+          <t>16/07/1964</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -2896,7 +3368,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 5.740,01</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2911,39 +3383,39 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 434,99</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 6.175,00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RJ - Magé</t>
+          <t>RJ - Queimados</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>05/01/2026 13:00</t>
+          <t>02/04/2026 09:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GIOVANNA DA COSTA CASTILHO</t>
+          <t>JOSIAS GOMES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>04/10/2018</t>
+          <t>26/12/1960</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO CIRURGIA GERAL</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -2951,7 +3423,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2971,34 +3443,34 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RJ - Magé</t>
+          <t>RJ - Queimados</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>05/01/2026 13:00</t>
+          <t>10/04/2026 14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LUIZ FELIPE ZARANZA DA SILVA</t>
+          <t>JOSIAS GOMES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>23/03/2021</t>
+          <t>26/12/1960</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO CIRURGIA GERAL</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -3006,7 +3478,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 7.439,81</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3021,39 +3493,39 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 692,19</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 8.132,00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RJ - Magé</t>
+          <t>RJ - Queimados</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10/01/2026 08:00</t>
+          <t>02/04/2026 07:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NYCOLAS SANCHES FIALHO</t>
+          <t>JOSIAS GOMES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23/06/2014</t>
+          <t>26/12/1960</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ORQUIDOPEXIA BILATERAL - PEDIATRICO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -3061,7 +3533,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>R$ 6.772,46</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3076,39 +3548,39 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>R$ 385,32</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>R$ 7.157,78</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RJ - Magé</t>
+          <t>RJ - Belford Roxo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17/01/2026 08:00</t>
+          <t>02/04/2026 09:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EMANUELLY VITORIA AZEVEDO MARTINS</t>
+          <t>NICE BATALHA RIBEIRO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>02/11/2018</t>
+          <t>12/12/1976</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -3116,7 +3588,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>R$ 6.514,54</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3131,39 +3603,39 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>R$ 1.183,81</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>R$ 7.698,35</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RJ - Magé</t>
+          <t>RJ - Belford Roxo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17/01/2026 08:00</t>
+          <t>09/04/2026 09:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JOSE BENICIO TOLEDO</t>
+          <t>RAYSSA SANTANA NASCIMENTO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>09/07/2024</t>
+          <t>05/08/2003</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ORQUIDOPEXIA BILATERAL - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -3171,7 +3643,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>R$ 6.772,46</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3186,39 +3658,39 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>R$ 385,32</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>R$ 7.157,78</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RJ - Magé</t>
+          <t>RJ - Belford Roxo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17/01/2026 08:00</t>
+          <t>09/04/2026 09:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GIOVANNA DA COSTA CASTILHO</t>
+          <t>THIAGO PEREIRA CASSIANO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>04/10/2018</t>
+          <t>29/10/2001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HERNIOPLASTIA UMBILICAL - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -3226,7 +3698,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>R$ 4.802,07</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3241,39 +3713,39 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>R$ 434,99</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>R$ 5.237,06</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RJ - Magé</t>
+          <t>RJ - Belford Roxo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17/01/2026 08:00</t>
+          <t>09/04/2026 09:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JOSE BENICIO TOLEDO</t>
+          <t>SOLANGE AGOSTINHO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>09/07/2024</t>
+          <t>28/01/1959</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>POSTECTOMIA - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -3281,7 +3753,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>R$ 4.630,88</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3296,39 +3768,39 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>R$ 219,12</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>R$ 4.850,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Belford Roxo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>05/01/2026 13:00</t>
+          <t>17/04/2026 09:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LORENZO ALVES TAVARES</t>
+          <t>RAYSSA SANTANA NASCIMENTO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>30/05/2022</t>
+          <t>05/08/2003</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -3336,7 +3808,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 7.439,81</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3351,39 +3823,39 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 692,19</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 8.132,00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Belford Roxo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10/01/2026 08:00</t>
+          <t>17/04/2026 09:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LORENZO ALVES TAVARES</t>
+          <t>THIAGO PEREIRA CASSIANO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>30/05/2022</t>
+          <t>29/10/2001</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -3391,7 +3863,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>R$ 6.514,54</t>
+          <t>R$ 7.439,81</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3406,39 +3878,39 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>R$ 1.183,81</t>
+          <t>R$ 692,19</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>R$ 7.698,35</t>
+          <t>R$ 8.132,00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RJ - Nova Iguaçu</t>
+          <t>RJ - Belford Roxo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10/01/2026 08:00</t>
+          <t>09/04/2026 09:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KEROLLAYNE VITORIA DA COSTA SILVA</t>
+          <t>SARA LINO DA SILVA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12/12/2014</t>
+          <t>28/11/1959</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HERNIOPLASTIA UMBILICAL - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -3446,7 +3918,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>R$ 4.802,07</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3461,39 +3933,39 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>R$ 434,99</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>R$ 5.237,06</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RJ - Queimados</t>
+          <t>RJ - Belford Roxo</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10/01/2026 08:00</t>
+          <t>09/04/2026 09:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PEDRO LUCCA BARBOSA RAMOS</t>
+          <t>JOANA D ARC MOURA DA SILVA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>04/04/2022</t>
+          <t>23/06/1965</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HERNIOPLASTIA INGUINAL (BILATERAL) - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -3501,7 +3973,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>R$ 5.239,94</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3516,39 +3988,39 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>R$ 610,06</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>R$ 5.850,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RJ - Queimados</t>
+          <t>RJ - Belford Roxo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10/01/2026 08:00</t>
+          <t>09/04/2026 09:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PIETRO COELHO DE AZEVEDO</t>
+          <t>MANOEL DA SILVA ARRUDA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>14/07/2019</t>
+          <t>05/11/1957</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ORQUIDOPEXIA BILATERAL - PEDIATRICO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -3556,7 +4028,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>R$ 6.772,46</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3571,39 +4043,39 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>R$ 385,32</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>R$ 7.157,78</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RJ - Seropédica</t>
+          <t>RJ - Belford Roxo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22/12/2025 15:00</t>
+          <t>17/04/2026 09:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CALEBE LEONARDO DA SILVA MACEDO DE SANTANA</t>
+          <t>SARA LINO DA SILVA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>08/07/2023</t>
+          <t>28/11/1959</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO PEDIÁTRICO OTORRINO</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -3611,7 +4083,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>R$ 290,00</t>
+          <t>R$ 7.439,81</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3626,39 +4098,39 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 692,19</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>R$ 300,00</t>
+          <t>R$ 8.132,00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RJ - Seropédica</t>
+          <t>RJ - Belford Roxo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14/01/2026 08:00</t>
+          <t>08/04/2026 07:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CALEBE LEONARDO DA SILVA MACEDO DE SANTANA</t>
+          <t>THIAGO PEREIRA CASSIANO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>08/07/2023</t>
+          <t>29/10/2001</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AMIGDALECTOMIA COM ADENOIDECTOMIA - PEDIATRICO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -3666,7 +4138,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>R$ 6.514,54</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3681,12 +4153,1552 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>R$ 1.183,81</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>R$ 7.698,35</t>
+          <t>R$ 400,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RJ - Belford Roxo</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>15/04/2026 07:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SARA LINO DA SILVA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>28/11/1959</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>R$ 400,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>RJ - Belford Roxo</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>09/04/2026 07:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>RAYSSA SANTANA NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>05/08/2003</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>R$ 400,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>RJ - Nilópolis</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>15/04/2026 07:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MILDNA BERNARDO REZENDE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>21/11/1961</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>R$ 400,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>RJ - Nilópolis</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>15/04/2026 07:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SUENIL DE OLIVEIRA GOMES</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>23/02/1952</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>R$ 400,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>RJ - Nilópolis</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>09/04/2026 07:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>RENATHA MENDES DA SILVA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>08/12/1978</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>R$ 400,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>RJ - Nilópolis</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>08/04/2026 16:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>RENATHA MENDES DA SILVA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>08/12/1978</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>R$ 440,00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>R$ 450,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>RJ - Nilópolis</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>15/04/2026 16:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SUENIL DE OLIVEIRA GOMES</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>23/02/1952</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>R$ 440,00</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>R$ 450,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>RJ - Nilópolis</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>15/04/2026 16:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>JOSE HENRIQUE RODRIGUES</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>18/03/1955</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>R$ 440,00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>R$ 450,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>RJ - Nilópolis</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>15/04/2026 16:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CHRISTIANE PEREIRA DA SILVA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>13/03/1974</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>R$ 440,00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>R$ 450,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>RJ - Nilópolis</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>15/04/2026 16:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MILDNA BERNARDO REZENDE</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>21/11/1961</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>R$ 440,00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>R$ 450,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>RJ - Nilópolis</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>18/04/2026 08:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MILDNA BERNARDO REZENDE</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>21/11/1961</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA INGUINAL (UNILATERAL) - ADULTO</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>R$ 5.212,03</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>R$ 637,97</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>R$ 5.850,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>RJ - Nilópolis</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>18/04/2026 08:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SUENIL DE OLIVEIRA GOMES</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>23/02/1952</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA INGUINAL (UNILATERAL) - ADULTO</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>R$ 5.212,03</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>R$ 637,97</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>R$ 5.850,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>RJ - Nilópolis</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>18/04/2026 08:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>RENATHA MENDES DA SILVA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>08/12/1978</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>R$ 12.107,55</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>R$ 992,45</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>R$ 13.100,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>RJ - Nilópolis</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>18/04/2026 08:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SUENIL DE OLIVEIRA GOMES</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>23/02/1952</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>R$ 5.740,01</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>R$ 434,99</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>R$ 6.175,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>RJ - Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>09/04/2026 07:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CLAUDIA LUCIA VIEIRA DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>22/09/1965</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>R$ 400,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>RJ - Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>09/04/2026 07:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>LEILA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>17/10/1956</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>R$ 400,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>RJ - Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>08/04/2026 16:00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>LEILA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>17/10/1956</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>R$ 440,00</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>R$ 450,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>RJ - Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>08/04/2026 16:00</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CLAUDIA LUCIA VIEIRA DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>22/09/1965</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>R$ 440,00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>R$ 450,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>RJ - Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>08/04/2026 16:00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CINTIA HONORATO SILVA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>15/01/1977</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>R$ 440,00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>R$ 450,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>RJ - Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>11/04/2026 08:00</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>LEILA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>17/10/1956</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>R$ 12.107,55</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>R$ 992,45</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>R$ 13.100,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>RJ - Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>11/04/2026 08:00</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CLAUDIA LUCIA VIEIRA DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>22/09/1965</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>R$ 12.107,55</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>R$ 992,45</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>R$ 13.100,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>RJ - Japeri</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>09/04/2026 07:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>LIDIANE PINTO ROSA GOUDARD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>05/05/1995</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>R$ 400,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>RJ - Japeri</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>09/04/2026 07:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>LEANDRO DA SILVA CONCEICAO</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>14/02/1980</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>R$ 400,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>RJ - Japeri</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>08/04/2026 16:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>LIDIANE PINTO ROSA GOUDARD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>05/05/1995</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>R$ 440,00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>R$ 450,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>RJ - Japeri</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>08/04/2026 16:00</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>LEANDRO DA SILVA CONCEICAO</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>14/02/1980</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>R$ 440,00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>R$ 450,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>RJ - Japeri</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>11/04/2026 08:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>LEANDRO DA SILVA CONCEICAO</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>14/02/1980</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>R$ 5.740,01</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>R$ 434,99</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>R$ 6.175,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>RJ - Japeri</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>11/04/2026 08:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>LEANDRO DA SILVA CONCEICAO</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>14/02/1980</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE HERNIOPLASTIA EPIGASTRICA - ADULTO</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>R$ 5.048,27</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>R$ 801,73</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>R$ 5.850,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>RJ - Japeri</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>18/04/2026 08:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>LIDIANE PINTO ROSA GOUDARD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>05/05/1995</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>R$ 12.107,55</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>R$ 992,45</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>R$ 13.100,00</t>
         </is>
       </c>
     </row>

--- a/relatorios_simplificados/separarNeotin_SIMPLIFICADO.xlsx
+++ b/relatorios_simplificados/separarNeotin_SIMPLIFICADO.xlsx
@@ -426,144 +426,129 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Paciente RJ - Mesquita</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RJ - Mesquita</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Quantidade RJ - Mesquita</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Paciente RJ - Queimados</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>RJ - Queimados</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Quantidade RJ - Queimados</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Paciente RJ - Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>RJ - Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Quantidade RJ - Nova Iguaçu</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Paciente RJ - Seropédica</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>RJ - Seropédica</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Quantidade RJ - Seropédica</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Paciente RJ - São João de Meriti</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>RJ - São João de Meriti</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Quantidade RJ - São João de Meriti</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Paciente RJ - Queimados</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>RJ - Queimados</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Quantidade RJ - Queimados</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Paciente RJ - Belford Roxo</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>RJ - Belford Roxo</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Quantidade RJ - Belford Roxo</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Paciente RJ - Nilópolis</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>RJ - Nilópolis</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Quantidade RJ - Nilópolis</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Paciente RJ - Nova Iguaçu</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>RJ - Nova Iguaçu</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Quantidade RJ - Nova Iguaçu</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Paciente RJ - Japeri</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>RJ - Japeri</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Quantidade RJ - Japeri</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MARIA NEILA DE SOUSA BARROS</t>
+          <t>REJANE DOS SANTOS MAXIMIANO ERMINIO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>EVILYN CABRIELLE RIBEIRO DE FREITAS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>JOSIAS GOMES DE OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SIMONE DA SILVA ARRUDA ARAUJO</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>NICE BATALHA RIBEIRO</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
-        </is>
-      </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>MILDNA BERNARDO REZENDE</t>
+          <t>MARCIA CRISTINA DOS SANTOS LIMA</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -576,120 +561,94 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CLAUDIA LUCIA VIEIRA DE SOUZA</t>
+          <t>ANA PAULA DE FIGUEIREDO SALES</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>CIRURGIA DE HISTERECTOMIA TOTAL - ADULTO</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>LIDIANE PINTO ROSA GOUDARD</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LIETE PEREIRA DE LIMA</t>
+          <t>REJANE DOS SANTOS MAXIMIANO ERMINIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DENILSON DA SILVA EVANGELISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MARIA ROSELMA FERNANDES DA SILVA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MARCIA CRISTINA DOS SANTOS LIMA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>JOSIAS GOMES DE OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>RAYSSA SANTANA NASCIMENTO</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>SUENIL DE OLIVEIRA GOMES</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
-        </is>
-      </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>LEILA DOS SANTOS</t>
+          <t>TADEU MARQUES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>CIRURGIA DE POSTECTOMIA (FIMOSE) - ADULTO</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>LEANDRO DA SILVA CONCEICAO</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NORMA FONSECA DOS SANTOS</t>
+          <t>REJANE DOS SANTOS MAXIMIANO ERMINIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -697,38 +656,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JOSIAS GOMES DE OLIVEIRA</t>
+          <t>DENILSON DA SILVA EVANGELISTA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>CIRURGIA DE VASECTOMIA - ADULTO</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MARIA ROSELMA FERNANDES DA SILVA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>THIAGO PEREIRA CASSIANO</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
-        </is>
-      </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>RENATHA MENDES DA SILVA</t>
+          <t>MARCIA CRISTINA DOS SANTOS LIMA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -736,51 +695,48 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>LEILA DOS SANTOS</t>
+          <t>TADEU MARQUES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - UROLOGIA</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>LIDIANE PINTO ROSA GOUDARD</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>REGINA FATIMA SILVA FERREIRA</t>
+          <t>SCHEILA SANTOS DA COSTA SILVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RAQUEL GUEDES DOS SANTOS FERREIRA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SOLANGE AGOSTINHO</t>
+          <t>ROSIMERE VITORIA BARBOSA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -793,12 +749,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>RENATHA MENDES DA SILVA</t>
+          <t>SIMONE RAMOS DE ABREU</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -806,51 +762,48 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CLAUDIA LUCIA VIEIRA DE SOUZA</t>
+          <t>TADEU MARQUES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>LEANDRO DA SILVA CONCEICAO</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MARIA NEILA DE SOUSA BARROS</t>
+          <t>SCHEILA SANTOS DA COSTA SILVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RAQUEL GUEDES DOS SANTOS FERREIRA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>RAYSSA SANTANA NASCIMENTO</t>
+          <t>JOSELAINE ANCHIETA DA SILVA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -859,11 +812,11 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SUENIL DE OLIVEIRA GOMES</t>
+          <t>SIMONE RAMOS DE ABREU</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -876,56 +829,53 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CINTIA HONORATO SILVA</t>
+          <t>ANA PAULA DE FIGUEIREDO SALES</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - GINECOLOGIA</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>LEANDRO DA SILVA CONCEICAO</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>REGINA FATIMA SILVA FERREIRA</t>
+          <t>SERGIO RICARDO TRINDADE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DENILSON DA SILVA EVANGELISTA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - UROLOGIA</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>THIAGO PEREIRA CASSIANO</t>
+          <t>JOSELAINE ANCHIETA DA SILVA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -933,12 +883,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>JOSE HENRIQUE RODRIGUES</t>
+          <t>SIMONE RAMOS DE ABREU</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -946,35 +896,22 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>LEILA DOS SANTOS</t>
+          <t>ANA PAULA DE FIGUEIREDO SALES</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>LEANDRO DA SILVA CONCEICAO</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>CIRURGIA DE HERNIOPLASTIA EPIGASTRICA - ADULTO</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MARIA NEILA DE SOUSA BARROS</t>
+          <t>SERGIO RICARDO TRINDADE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -985,17 +922,27 @@
       <c r="C8" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EVILYN CABRIELLE RIBEIRO DE FREITAS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SARA LINO DA SILVA</t>
+          <t>JOSELAINE ANCHIETA DA SILVA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1003,64 +950,51 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>CHRISTIANE PEREIRA DA SILVA</t>
+          <t>ANTONIO SINHORINHO</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>CLAUDIA LUCIA VIEIRA DE SOUZA</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>LIDIANE PINTO ROSA GOUDARD</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REGINA FATIMA SILVA FERREIRA</t>
+          <t>ANA MARIA ARAUJO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EVILYN CABRIELLE RIBEIRO DE FREITAS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>JOANA D ARC MOURA DA SILVA</t>
+          <t>MARGARETE DA SILVA FARIAS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1073,7 +1007,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>MILDNA BERNARDO REZENDE</t>
+          <t>ANTONIO SINHORINHO</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1087,14 +1021,11 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JOSE ROBSON DA SILVA</t>
+          <t>ANA MARIA ARAUJO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1105,17 +1036,27 @@
       <c r="C10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RAQUEL GUEDES DOS SANTOS FERREIRA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MANOEL DA SILVA ARRUDA</t>
+          <t>AIRTON GERALDO CAMARGO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1123,12 +1064,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>MILDNA BERNARDO REZENDE</t>
+          <t>ANTONIO SINHORINHO</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA INGUINAL (UNILATERAL) - ADULTO</t>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1137,19 +1078,16 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MARCELO RIBEIRO DA SILVA</t>
+          <t>RUBENS LEONARDO COELHO DOS SANTOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1160,41 +1098,28 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SARA LINO DA SILVA</t>
+          <t>AIRTON GERALDO CAMARGO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - UROLOGIA</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>SUENIL DE OLIVEIRA GOMES</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>CIRURGIA DE HERNIOPLASTIA INGUINAL (UNILATERAL) - ADULTO</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CELIA DOS SANTOS PEDREIRO</t>
+          <t>RUBENS LEONARDO COELHO DOS SANTOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1210,41 +1135,28 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>THIAGO PEREIRA CASSIANO</t>
+          <t>AIRTON GERALDO CAMARGO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>CIRURGIA DE POSTECTOMIA (FIMOSE) - ADULTO</t>
         </is>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>RENATHA MENDES DA SILVA</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SUELI DO AMARAL RIBEIRO</t>
+          <t>FABIANA DA SILVA TOSTA DA SILVA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1260,46 +1172,33 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SARA LINO DA SILVA</t>
+          <t>MARCOS VINICIUS LEMOS ACCIOLI</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - UROLOGIA</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>SUENIL DE OLIVEIRA GOMES</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FRANCISCO DAS CHAGAS MORAIS</t>
+          <t>FABIANA DA SILVA TOSTA DA SILVA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1310,12 +1209,12 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>RAYSSA SANTANA NASCIMENTO</t>
+          <t>JOSE MAXIMO PEREIRA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - UROLOGIA</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1327,19 +1226,16 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ROZANA FERREIRA EGIDIO ALVES PINTO</t>
+          <t>FABIANA DA SILVA TOSTA DA SILVA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1348,28 +1244,35 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>JOSE MAXIMO PEREIRA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VALQUIRIA DOS SANTOS SILVA</t>
+          <t>ROSANGELA DE OLIVEIRA LIMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1378,28 +1281,35 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>JOSE MAXIMO PEREIRA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE POSTECTOMIA (FIMOSE) - ADULTO</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MARIA DE LOURDES DE SA VIANA</t>
+          <t>ROSANGELA DE OLIVEIRA LIMA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1408,28 +1318,35 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MARIA ROSELMA FERNANDES DA SILVA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JOSE ROBSON DA SILVA</t>
+          <t>ROSANGELA DE OLIVEIRA LIMA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1447,19 +1364,16 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MARCELO RIBEIRO DA SILVA</t>
+          <t>GLAUCIA DE OLIVEIRA MELLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1477,19 +1391,16 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ROZANA FERREIRA EGIDIO ALVES PINTO</t>
+          <t>GLAUCIA DE OLIVEIRA MELLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1507,23 +1418,20 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SUELI DO AMARAL RIBEIRO</t>
+          <t>GLAUCIA DE OLIVEIRA MELLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1537,19 +1445,16 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FRANCISCO DAS CHAGAS MORAIS</t>
+          <t>LILIAN ALVES COELHO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1567,19 +1472,16 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CELIA DOS SANTOS PEDREIRO</t>
+          <t>LILIAN ALVES COELHO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1597,19 +1499,16 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CELIA DOS SANTOS PEDREIRO</t>
+          <t>EMANOEL ANTONIO BASILIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - UROLOGIA</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1627,19 +1526,16 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FRANCISCO DAS CHAGAS MORAIS</t>
+          <t>EMANOEL ANTONIO BASILIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA INCISIONAL - ADULTO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1657,19 +1553,16 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SUELI DO AMARAL RIBEIRO</t>
+          <t>EMANOEL ANTONIO BASILIO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+          <t>CIRURGIA DE RESSECÇÃO ENDOSCÓPICA DE PRÓSTATA - ADULTO</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1687,19 +1580,16 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ROZANA FERREIRA EGIDIO ALVES PINTO</t>
+          <t>ALESSANDRA LEITE DE SANTANA DE VASCONCELOS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - GINECOLOGIA</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1717,19 +1607,16 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MARCELO RIBEIRO DA SILVA</t>
+          <t>ALESSANDRA LEITE DE SANTANA DE VASCONCELOS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA INCISIONAL - ADULTO</t>
+          <t>CIRURGIA DE HISTERECTOMIA TOTAL - ADULTO</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1747,19 +1634,16 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JOSE ROBSON DA SILVA</t>
+          <t>ALESSANDRA LEITE DE SANTANA DE VASCONCELOS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1777,9 +1661,114 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SERGIO RICARDO TRINDADE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RUBENS LEONARDO COELHO DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ANA MARIA ARAUJO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LILIAN ALVES COELHO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1792,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1855,35 +1844,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>02/04/2026 13:30</t>
+          <t>03/04/2026 08:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MARIA NEILA DE SOUSA BARROS</t>
+          <t>REJANE DOS SANTOS MAXIMIANO ERMINIO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>01/05/1978</t>
+          <t>06/08/1977</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 14.879,62</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1898,39 +1887,39 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 1.384,38</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 16.264,00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>02/04/2026 13:30</t>
+          <t>20/03/2026 14:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LIETE PEREIRA DE LIMA</t>
+          <t>REJANE DOS SANTOS MAXIMIANO ERMINIO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>29/03/1951</t>
+          <t>06/08/1977</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1965,27 +1954,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>02/04/2026 13:30</t>
+          <t>23/03/2026 09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NORMA FONSECA DOS SANTOS</t>
+          <t>REJANE DOS SANTOS MAXIMIANO ERMINIO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05/07/1960</t>
+          <t>06/08/1977</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1993,7 +1982,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2013,34 +2002,34 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>02/04/2026 13:30</t>
+          <t>23/03/2026 09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REGINA FATIMA SILVA FERREIRA</t>
+          <t>SCHEILA SANTOS DA COSTA SILVA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11/03/1962</t>
+          <t>18/02/1969</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -2048,7 +2037,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2068,34 +2057,34 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14/04/2026 10:00</t>
+          <t>20/03/2026 14:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MARIA NEILA DE SOUSA BARROS</t>
+          <t>SCHEILA SANTOS DA COSTA SILVA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>01/05/1978</t>
+          <t>18/02/1969</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -2103,7 +2092,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>R$ 5.740,01</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2118,39 +2107,39 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>R$ 434,99</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R$ 6.175,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14/04/2026 10:00</t>
+          <t>20/03/2026 14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>REGINA FATIMA SILVA FERREIRA</t>
+          <t>SERGIO RICARDO TRINDADE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11/03/1962</t>
+          <t>30/09/1961</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -2158,7 +2147,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>R$ 5.740,01</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2173,34 +2162,34 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>R$ 434,99</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R$ 6.175,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>02/04/2026 07:00</t>
+          <t>24/03/2026 14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MARIA NEILA DE SOUSA BARROS</t>
+          <t>SERGIO RICARDO TRINDADE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>01/05/1978</t>
+          <t>30/09/1961</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2240,27 +2229,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>02/04/2026 07:00</t>
+          <t>20/03/2026 14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>REGINA FATIMA SILVA FERREIRA</t>
+          <t>ANA MARIA ARAUJO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11/03/1962</t>
+          <t>18/01/1970</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2268,7 +2257,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2288,29 +2277,29 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>R$ 400,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>08/04/2026 07:00</t>
+          <t>24/03/2026 14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JOSE ROBSON DA SILVA</t>
+          <t>ANA MARIA ARAUJO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16/07/1964</t>
+          <t>18/01/1970</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2350,27 +2339,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>08/04/2026 07:00</t>
+          <t>20/03/2026 14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MARCELO RIBEIRO DA SILVA</t>
+          <t>RUBENS LEONARDO COELHO DOS SANTOS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>05/05/1979</t>
+          <t>14/02/1984</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2378,7 +2367,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2398,29 +2387,29 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R$ 400,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09/04/2026 07:00</t>
+          <t>24/03/2026 14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CELIA DOS SANTOS PEDREIRO</t>
+          <t>RUBENS LEONARDO COELHO DOS SANTOS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>31/12/1962</t>
+          <t>14/02/1984</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2460,22 +2449,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09/04/2026 07:00</t>
+          <t>30/03/2026 09:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SUELI DO AMARAL RIBEIRO</t>
+          <t>FABIANA DA SILVA TOSTA DA SILVA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24/04/1963</t>
+          <t>15/03/1984</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2515,27 +2504,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09/04/2026 07:00</t>
+          <t>20/03/2026 14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FRANCISCO DAS CHAGAS MORAIS</t>
+          <t>FABIANA DA SILVA TOSTA DA SILVA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17/11/1963</t>
+          <t>15/03/1984</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2543,7 +2532,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2563,34 +2552,34 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R$ 400,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09/04/2026 07:00</t>
+          <t>17/04/2026 08:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ROZANA FERREIRA EGIDIO ALVES PINTO</t>
+          <t>FABIANA DA SILVA TOSTA DA SILVA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30/11/1963</t>
+          <t>15/03/1984</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -2598,7 +2587,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
+          <t>R$ 7.439,81</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2613,39 +2602,39 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 692,19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R$ 400,00</t>
+          <t>R$ 8.132,00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01/04/2026 16:00</t>
+          <t>20/03/2026 14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VALQUIRIA DOS SANTOS SILVA</t>
+          <t>ROSANGELA DE OLIVEIRA LIMA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19/11/1976</t>
+          <t>16/10/1974</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -2680,27 +2669,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01/04/2026 16:00</t>
+          <t>30/03/2026 09:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MARIA DE LOURDES DE SA VIANA</t>
+          <t>ROSANGELA DE OLIVEIRA LIMA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>28/08/1965</t>
+          <t>16/10/1974</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2708,7 +2697,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2728,34 +2717,34 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01/04/2026 16:00</t>
+          <t>17/04/2026 08:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JOSE ROBSON DA SILVA</t>
+          <t>ROSANGELA DE OLIVEIRA LIMA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16/07/1964</t>
+          <t>16/10/1974</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2763,7 +2752,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 7.439,81</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2778,39 +2767,39 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 692,19</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 8.132,00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01/04/2026 16:00</t>
+          <t>20/03/2026 14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MARCELO RIBEIRO DA SILVA</t>
+          <t>GLAUCIA DE OLIVEIRA MELLO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>05/05/1979</t>
+          <t>13/09/1988</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -2845,27 +2834,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>08/04/2026 16:00</t>
+          <t>30/03/2026 09:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ROZANA FERREIRA EGIDIO ALVES PINTO</t>
+          <t>GLAUCIA DE OLIVEIRA MELLO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30/11/1963</t>
+          <t>13/09/1988</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -2873,7 +2862,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2893,42 +2882,42 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>08/04/2026 16:00</t>
+          <t>17/04/2026 08:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUELI DO AMARAL RIBEIRO</t>
+          <t>GLAUCIA DE OLIVEIRA MELLO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>24/04/1963</t>
+          <t>13/09/1988</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 14.879,62</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2943,39 +2932,39 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 1.384,38</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 16.264,00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>08/04/2026 16:00</t>
+          <t>30/03/2026 09:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FRANCISCO DAS CHAGAS MORAIS</t>
+          <t>LILIAN ALVES COELHO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17/11/1963</t>
+          <t>27/01/1967</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2983,7 +2972,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3003,34 +2992,34 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>08/04/2026 16:00</t>
+          <t>20/03/2026 14:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CELIA DOS SANTOS PEDREIRO</t>
+          <t>LILIAN ALVES COELHO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>31/12/1962</t>
+          <t>27/01/1967</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -3065,27 +3054,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17/04/2026 08:00</t>
+          <t>23/03/2026 08:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CELIA DOS SANTOS PEDREIRO</t>
+          <t>EMANOEL ANTONIO BASILIO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>31/12/1962</t>
+          <t>01/11/1944</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - UROLOGIA</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -3093,7 +3082,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R$ 5.740,01</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3108,39 +3097,39 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>R$ 434,99</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>R$ 6.175,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17/04/2026 08:00</t>
+          <t>30/03/2026 09:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FRANCISCO DAS CHAGAS MORAIS</t>
+          <t>EMANOEL ANTONIO BASILIO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17/11/1963</t>
+          <t>01/11/1944</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA INCISIONAL - ADULTO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -3148,7 +3137,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>R$ 5.635,08</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3163,39 +3152,39 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>R$ 539,92</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>R$ 6.175,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17/04/2026 08:00</t>
+          <t>05/04/2026 08:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUELI DO AMARAL RIBEIRO</t>
+          <t>EMANOEL ANTONIO BASILIO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>24/04/1963</t>
+          <t>01/11/1944</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+          <t>CIRURGIA DE RESSECÇÃO ENDOSCÓPICA DE PRÓSTATA - ADULTO</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -3203,7 +3192,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>R$ 5.740,01</t>
+          <t>R$ 13.648,42</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3218,39 +3207,39 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>R$ 434,99</t>
+          <t>R$ 851,58</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>R$ 6.175,00</t>
+          <t>R$ 14.500,00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17/04/2026 08:00</t>
+          <t>20/03/2026 13:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ROZANA FERREIRA EGIDIO ALVES PINTO</t>
+          <t>ALESSANDRA LEITE DE SANTANA DE VASCONCELOS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>30/11/1963</t>
+          <t>20/11/1981</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - GINECOLOGIA</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -3258,7 +3247,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>R$ 5.740,01</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3273,39 +3262,39 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>R$ 434,99</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>R$ 6.175,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10/04/2026 11:11</t>
+          <t>01/04/2026 13:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MARCELO RIBEIRO DA SILVA</t>
+          <t>ALESSANDRA LEITE DE SANTANA DE VASCONCELOS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>05/05/1979</t>
+          <t>20/11/1981</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA INCISIONAL - ADULTO</t>
+          <t>CIRURGIA DE HISTERECTOMIA TOTAL - ADULTO</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -3313,7 +3302,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>R$ 5.635,08</t>
+          <t>R$ 9.782,56</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3328,39 +3317,39 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>R$ 539,92</t>
+          <t>R$ 1.103,64</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>R$ 6.175,00</t>
+          <t>R$ 10.886,20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RJ - São João de Meriti</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18/04/2026 08:00</t>
+          <t>31/03/2026 09:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JOSE ROBSON DA SILVA</t>
+          <t>ALESSANDRA LEITE DE SANTANA DE VASCONCELOS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>16/07/1964</t>
+          <t>20/11/1981</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -3368,7 +3357,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>R$ 5.740,01</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3383,47 +3372,47 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>R$ 434,99</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>R$ 6.175,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RJ - Queimados</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>02/04/2026 09:00</t>
+          <t>10/04/2026 08:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>JOSIAS GOMES DE OLIVEIRA</t>
+          <t>SERGIO RICARDO TRINDADE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26/12/1960</t>
+          <t>30/09/1961</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 14.879,62</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3438,34 +3427,34 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 1.384,38</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 16.264,00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RJ - Queimados</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10/04/2026 14:00</t>
+          <t>10/04/2026 08:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JOSIAS GOMES DE OLIVEIRA</t>
+          <t>RUBENS LEONARDO COELHO DOS SANTOS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26/12/1960</t>
+          <t>14/02/1984</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3474,11 +3463,11 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>R$ 7.439,81</t>
+          <t>R$ 14.879,62</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3493,47 +3482,47 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>R$ 692,19</t>
+          <t>R$ 1.384,38</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>R$ 8.132,00</t>
+          <t>R$ 16.264,00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RJ - Queimados</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>02/04/2026 07:00</t>
+          <t>10/04/2026 08:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JOSIAS GOMES DE OLIVEIRA</t>
+          <t>ANA MARIA ARAUJO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>26/12/1960</t>
+          <t>18/01/1970</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
+          <t>R$ 14.879,62</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3548,47 +3537,47 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 1.384,38</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>R$ 400,00</t>
+          <t>R$ 16.264,00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - Mesquita</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>02/04/2026 09:00</t>
+          <t>17/04/2026 08:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NICE BATALHA RIBEIRO</t>
+          <t>LILIAN ALVES COELHO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12/12/1976</t>
+          <t>27/01/1967</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 14.879,62</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3603,39 +3592,39 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 1.384,38</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 16.264,00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - Queimados</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>09/04/2026 09:00</t>
+          <t>27/03/2026 13:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RAYSSA SANTANA NASCIMENTO</t>
+          <t>EVILYN CABRIELLE RIBEIRO DE FREITAS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>05/08/2003</t>
+          <t>02/10/2006</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -3670,27 +3659,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - Queimados</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>09/04/2026 09:00</t>
+          <t>27/03/2026 09:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>THIAGO PEREIRA CASSIANO</t>
+          <t>DENILSON DA SILVA EVANGELISTA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>29/10/2001</t>
+          <t>06/02/1983</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -3698,7 +3687,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3718,34 +3707,34 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - Queimados</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>09/04/2026 09:00</t>
+          <t>05/04/2026 08:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SOLANGE AGOSTINHO</t>
+          <t>DENILSON DA SILVA EVANGELISTA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>28/01/1959</t>
+          <t>06/02/1983</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
+          <t>CIRURGIA DE VASECTOMIA - ADULTO</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -3753,7 +3742,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 5.411,13</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3768,39 +3757,39 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 438,87</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 5.850,00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - Queimados</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17/04/2026 09:00</t>
+          <t>27/03/2026 13:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RAYSSA SANTANA NASCIMENTO</t>
+          <t>RAQUEL GUEDES DOS SANTOS FERREIRA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>05/08/2003</t>
+          <t>01/07/1982</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -3808,7 +3797,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>R$ 7.439,81</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3823,39 +3812,39 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>R$ 692,19</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>R$ 8.132,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - Queimados</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17/04/2026 09:00</t>
+          <t>27/03/2026 09:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>THIAGO PEREIRA CASSIANO</t>
+          <t>RAQUEL GUEDES DOS SANTOS FERREIRA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>29/10/2001</t>
+          <t>01/07/1982</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -3863,7 +3852,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>R$ 7.439,81</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3878,39 +3867,39 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>R$ 692,19</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>R$ 8.132,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - Queimados</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>09/04/2026 09:00</t>
+          <t>27/03/2026 09:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SARA LINO DA SILVA</t>
+          <t>DENILSON DA SILVA EVANGELISTA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>28/11/1959</t>
+          <t>06/02/1983</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - UROLOGIA</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -3945,27 +3934,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - Queimados</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>09/04/2026 09:00</t>
+          <t>27/03/2026 09:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JOANA D ARC MOURA DA SILVA</t>
+          <t>EVILYN CABRIELLE RIBEIRO DE FREITAS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>23/06/1965</t>
+          <t>02/10/2006</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -3973,7 +3962,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3993,34 +3982,34 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - Queimados</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>09/04/2026 09:00</t>
+          <t>04/04/2026 08:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MANOEL DA SILVA ARRUDA</t>
+          <t>EVILYN CABRIELLE RIBEIRO DE FREITAS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>05/11/1957</t>
+          <t>02/10/2006</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -4028,7 +4017,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 12.107,55</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4043,39 +4032,39 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 992,45</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 13.100,00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - Queimados</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17/04/2026 09:00</t>
+          <t>04/04/2026 08:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SARA LINO DA SILVA</t>
+          <t>RAQUEL GUEDES DOS SANTOS FERREIRA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>28/11/1959</t>
+          <t>01/07/1982</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -4083,7 +4072,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>R$ 7.439,81</t>
+          <t>R$ 12.107,55</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4098,39 +4087,39 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>R$ 692,19</t>
+          <t>R$ 992,45</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>R$ 8.132,00</t>
+          <t>R$ 13.100,00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>08/04/2026 07:00</t>
+          <t>20/03/2026 14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>THIAGO PEREIRA CASSIANO</t>
+          <t>SIMONE DA SILVA ARRUDA ARAUJO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>29/10/2001</t>
+          <t>07/09/1973</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -4138,7 +4127,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4158,34 +4147,34 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>R$ 400,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15/04/2026 07:00</t>
+          <t>20/03/2026 14:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SARA LINO DA SILVA</t>
+          <t>MARIA ROSELMA FERNANDES DA SILVA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>28/11/1959</t>
+          <t>27/09/1968</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -4193,7 +4182,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4213,29 +4202,29 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>R$ 400,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RJ - Belford Roxo</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>09/04/2026 07:00</t>
+          <t>27/03/2026 09:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RAYSSA SANTANA NASCIMENTO</t>
+          <t>MARIA ROSELMA FERNANDES DA SILVA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>05/08/2003</t>
+          <t>27/09/1968</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4275,27 +4264,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15/04/2026 07:00</t>
+          <t>20/03/2026 14:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MILDNA BERNARDO REZENDE</t>
+          <t>ROSIMERE VITORIA BARBOSA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>21/11/1961</t>
+          <t>02/03/1974</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -4303,7 +4292,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4323,42 +4312,42 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>R$ 400,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15/04/2026 07:00</t>
+          <t>10/04/2026 08:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SUENIL DE OLIVEIRA GOMES</t>
+          <t>JOSELAINE ANCHIETA DA SILVA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>23/02/1952</t>
+          <t>12/10/1979</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
+          <t>R$ 14.879,62</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4373,39 +4362,39 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 1.384,38</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>R$ 400,00</t>
+          <t>R$ 16.264,00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>09/04/2026 07:00</t>
+          <t>20/03/2026 14:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RENATHA MENDES DA SILVA</t>
+          <t>JOSELAINE ANCHIETA DA SILVA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>08/12/1978</t>
+          <t>12/10/1979</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -4413,7 +4402,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4433,34 +4422,34 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>R$ 400,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>08/04/2026 16:00</t>
+          <t>27/03/2026 09:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>RENATHA MENDES DA SILVA</t>
+          <t>JOSELAINE ANCHIETA DA SILVA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>08/12/1978</t>
+          <t>12/10/1979</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -4468,7 +4457,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4488,34 +4477,34 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15/04/2026 16:00</t>
+          <t>20/03/2026 14:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SUENIL DE OLIVEIRA GOMES</t>
+          <t>MARGARETE DA SILVA FARIAS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>23/02/1952</t>
+          <t>16/08/1955</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - VASCULAR</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -4550,27 +4539,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15/04/2026 16:00</t>
+          <t>27/03/2026 09:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JOSE HENRIQUE RODRIGUES</t>
+          <t>AIRTON GERALDO CAMARGO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>18/03/1955</t>
+          <t>08/05/1959</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -4578,7 +4567,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4598,34 +4587,34 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15/04/2026 16:00</t>
+          <t>23/03/2026 08:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CHRISTIANE PEREIRA DA SILVA</t>
+          <t>AIRTON GERALDO CAMARGO</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>13/03/1974</t>
+          <t>08/05/1959</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - UROLOGIA</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -4660,27 +4649,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15/04/2026 16:00</t>
+          <t>05/04/2026 08:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MILDNA BERNARDO REZENDE</t>
+          <t>AIRTON GERALDO CAMARGO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>21/11/1961</t>
+          <t>08/05/1959</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>CIRURGIA DE POSTECTOMIA (FIMOSE) - ADULTO</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -4688,7 +4677,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 5.630,88</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4703,39 +4692,39 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 219,12</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 5.850,00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>18/04/2026 08:00</t>
+          <t>23/03/2026 08:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MILDNA BERNARDO REZENDE</t>
+          <t>MARCOS VINICIUS LEMOS ACCIOLI</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>21/11/1961</t>
+          <t>28/03/1980</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA INGUINAL (UNILATERAL) - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - UROLOGIA</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -4743,7 +4732,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>R$ 5.212,03</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4758,39 +4747,39 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>R$ 637,97</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>R$ 5.850,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>18/04/2026 08:00</t>
+          <t>23/03/2026 08:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SUENIL DE OLIVEIRA GOMES</t>
+          <t>JOSE MAXIMO PEREIRA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>23/02/1952</t>
+          <t>05/07/1943</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA INGUINAL (UNILATERAL) - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - UROLOGIA</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -4798,7 +4787,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>R$ 5.212,03</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4813,39 +4802,39 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>R$ 637,97</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>R$ 5.850,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>18/04/2026 08:00</t>
+          <t>27/03/2026 09:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RENATHA MENDES DA SILVA</t>
+          <t>JOSE MAXIMO PEREIRA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>08/12/1978</t>
+          <t>05/07/1943</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -4853,7 +4842,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>R$ 12.107,55</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4868,39 +4857,39 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>R$ 992,45</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>R$ 13.100,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RJ - Nilópolis</t>
+          <t>RJ - Nova Iguaçu</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>18/04/2026 08:00</t>
+          <t>11/04/2026 08:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SUENIL DE OLIVEIRA GOMES</t>
+          <t>JOSE MAXIMO PEREIRA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>23/02/1952</t>
+          <t>05/07/1943</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+          <t>CIRURGIA DE POSTECTOMIA (FIMOSE) - ADULTO</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -4908,7 +4897,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>R$ 5.740,01</t>
+          <t>R$ 5.630,88</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4923,12 +4912,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>R$ 434,99</t>
+          <t>R$ 219,12</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>R$ 6.175,00</t>
+          <t>R$ 5.850,00</t>
         </is>
       </c>
     </row>
@@ -4940,30 +4929,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>09/04/2026 07:00</t>
+          <t>03/04/2026 08:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CLAUDIA LUCIA VIEIRA DE SOUZA</t>
+          <t>MARIA ROSELMA FERNANDES DA SILVA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>22/09/1965</t>
+          <t>27/09/1968</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>CIRURGIA DE VARIZES UNILATERAL (COM SAFENA) - ADULTO</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
+          <t>R$ 14.879,62</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4978,34 +4967,34 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 1.384,38</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>R$ 400,00</t>
+          <t>R$ 16.264,00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RJ - Nova Iguaçu</t>
+          <t>RJ - Seropédica</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>09/04/2026 07:00</t>
+          <t>27/03/2026 09:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LEILA DOS SANTOS</t>
+          <t>MARCIA CRISTINA DOS SANTOS LIMA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>17/10/1956</t>
+          <t>22/08/1973</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5045,22 +5034,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RJ - Nova Iguaçu</t>
+          <t>RJ - Seropédica</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>08/04/2026 16:00</t>
+          <t>27/03/2026 13:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LEILA DOS SANTOS</t>
+          <t>MARCIA CRISTINA DOS SANTOS LIMA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>17/10/1956</t>
+          <t>22/08/1973</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5100,27 +5089,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RJ - Nova Iguaçu</t>
+          <t>RJ - Seropédica</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>08/04/2026 16:00</t>
+          <t>04/04/2026 08:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CLAUDIA LUCIA VIEIRA DE SOUZA</t>
+          <t>MARCIA CRISTINA DOS SANTOS LIMA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>22/09/1965</t>
+          <t>22/08/1973</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -5128,7 +5117,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 12.107,55</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5143,39 +5132,39 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 992,45</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 13.100,00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>RJ - Nova Iguaçu</t>
+          <t>RJ - Seropédica</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>08/04/2026 16:00</t>
+          <t>05/04/2026 08:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CINTIA HONORATO SILVA</t>
+          <t>SIMONE RAMOS DE ABREU</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>15/01/1977</t>
+          <t>23/01/1970</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -5183,7 +5172,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 12.107,55</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5198,39 +5187,39 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 992,45</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 13.100,00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>RJ - Nova Iguaçu</t>
+          <t>RJ - Seropédica</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11/04/2026 08:00</t>
+          <t>27/03/2026 13:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LEILA DOS SANTOS</t>
+          <t>SIMONE RAMOS DE ABREU</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>17/10/1956</t>
+          <t>23/01/1970</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -5238,7 +5227,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>R$ 12.107,55</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5253,39 +5242,39 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>R$ 992,45</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>R$ 13.100,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>RJ - Nova Iguaçu</t>
+          <t>RJ - Seropédica</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11/04/2026 08:00</t>
+          <t>27/03/2026 09:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CLAUDIA LUCIA VIEIRA DE SOUZA</t>
+          <t>SIMONE RAMOS DE ABREU</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>22/09/1965</t>
+          <t>23/01/1970</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -5293,7 +5282,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>R$ 12.107,55</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5308,34 +5297,34 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>R$ 992,45</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>R$ 13.100,00</t>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>RJ - Japeri</t>
+          <t>RJ - Seropédica</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>09/04/2026 07:00</t>
+          <t>27/03/2026 09:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LIDIANE PINTO ROSA GOUDARD</t>
+          <t>ANTONIO SINHORINHO</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>05/05/1995</t>
+          <t>13/06/1955</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5375,27 +5364,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RJ - Japeri</t>
+          <t>RJ - Seropédica</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>09/04/2026 07:00</t>
+          <t>27/03/2026 13:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LEANDRO DA SILVA CONCEICAO</t>
+          <t>ANTONIO SINHORINHO</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>14/02/1980</t>
+          <t>13/06/1955</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -5403,7 +5392,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>R$ 390,00</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5423,34 +5412,34 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>R$ 400,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>RJ - Japeri</t>
+          <t>RJ - Seropédica</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>08/04/2026 16:00</t>
+          <t>04/04/2026 08:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LIDIANE PINTO ROSA GOUDARD</t>
+          <t>ANTONIO SINHORINHO</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>05/05/1995</t>
+          <t>13/06/1955</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -5458,7 +5447,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 12.107,55</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5473,39 +5462,39 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 992,45</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 13.100,00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RJ - Japeri</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>08/04/2026 16:00</t>
+          <t>01/04/2026 13:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LEANDRO DA SILVA CONCEICAO</t>
+          <t>ANA PAULA DE FIGUEIREDO SALES</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>14/02/1980</t>
+          <t>07/03/1990</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PACOTE PRÉ-OPERATÓRIO ADULTO CIRURGIA GERAL</t>
+          <t>CIRURGIA DE HISTERECTOMIA TOTAL - ADULTO</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -5513,7 +5502,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>R$ 440,00</t>
+          <t>R$ 9.782,56</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5528,19 +5517,19 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>R$ 10,00</t>
+          <t>R$ 1.103,64</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>R$ 450,00</t>
+          <t>R$ 10.886,20</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RJ - Japeri</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5550,17 +5539,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LEANDRO DA SILVA CONCEICAO</t>
+          <t>TADEU MARQUES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>14/02/1980</t>
+          <t>10/07/1991</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA UMBILICAL - ADULTO</t>
+          <t>CIRURGIA DE POSTECTOMIA (FIMOSE) - ADULTO</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -5568,7 +5557,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>R$ 5.740,01</t>
+          <t>R$ 5.630,88</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5583,39 +5572,39 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>R$ 434,99</t>
+          <t>R$ 219,12</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>R$ 6.175,00</t>
+          <t>R$ 5.850,00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RJ - Japeri</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11/04/2026 08:00</t>
+          <t>31/03/2026 14:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LEANDRO DA SILVA CONCEICAO</t>
+          <t>TADEU MARQUES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>14/02/1980</t>
+          <t>10/07/1991</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CIRURGIA DE HERNIOPLASTIA EPIGASTRICA - ADULTO</t>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - UROLOGIA</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -5623,7 +5612,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>R$ 5.048,27</t>
+          <t>R$ 440,00</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5638,39 +5627,39 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>R$ 801,73</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>R$ 5.850,00</t>
+          <t>R$ 450,00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RJ - Japeri</t>
+          <t>RJ - São João de Meriti</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>18/04/2026 08:00</t>
+          <t>31/03/2026 09:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LIDIANE PINTO ROSA GOUDARD</t>
+          <t>TADEU MARQUES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>05/05/1995</t>
+          <t>10/07/1991</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CIRURGIA DE COLECISTECTOMIA VIDEOLAPAROSCÓPICA - ADULTO</t>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -5678,7 +5667,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>R$ 12.107,55</t>
+          <t>R$ 390,00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5693,12 +5682,122 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>R$ 992,45</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>R$ 13.100,00</t>
+          <t>R$ 400,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>RJ - São João de Meriti</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>27/03/2026 09:00</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ANA PAULA DE FIGUEIREDO SALES</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>07/03/1990</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PACOTE PRÉ-OPERATÓRIO ADULTO - GINECOLOGIA</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>R$ 440,00</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>R$ 450,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>RJ - São João de Meriti</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>31/03/2026 09:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ANA PAULA DE FIGUEIREDO SALES</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>07/03/1990</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PACOTE RISCO CIRURGICO - ADULTO</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>R$ 390,00</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>R$ 400,00</t>
         </is>
       </c>
     </row>
